--- a/data/b2_bonsucesso/B2 Bonsucesso 04-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 04-2026.xlsx
@@ -4658,7 +4658,7 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46116</v>
+        <v>46115</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
@@ -4667,29 +4667,29 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1440.85</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46117</v>
+        <v>46116</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>65023.6</v>
+        <v>1834.9</v>
       </c>
     </row>
     <row r="4">
@@ -4698,39 +4698,39 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2848.87</v>
+        <v>65313.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46122</v>
+        <v>46117</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>2870.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46124</v>
+        <v>46118</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -4739,173 +4739,173 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>795.51</v>
+        <v>1235.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46124</v>
+        <v>46120</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4031.01</v>
+        <v>3938.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46124</v>
+        <v>46122</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1427.11</v>
+        <v>1406.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2841.42</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46127</v>
+        <v>46124</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10167.55</v>
+        <v>4223.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46127</v>
+        <v>46124</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2031.37</v>
+        <v>1283.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46129</v>
+        <v>46127</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3120.83</v>
+        <v>9607.790000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46131</v>
+        <v>46127</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>4088.87</v>
+        <v>1793.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46132</v>
+        <v>46131</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>22825.65</v>
+        <v>4147.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46138</v>
+        <v>46132</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1219.16</v>
+        <v>23110.52</v>
       </c>
     </row>
     <row r="16">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3774.09</v>
+        <v>3811.39</v>
       </c>
     </row>
     <row r="17">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2288.74</v>
+        <v>2342.32</v>
       </c>
     </row>
   </sheetData>
